--- a/data/evaluation/Experiment.xlsx
+++ b/data/evaluation/Experiment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github_ThisPC\muict_thai_legal_rag\data\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459587A2-470C-4F72-A248-BA045A247776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCA63C1-23B3-4249-9096-9B24C36CBD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>system</t>
   </si>
@@ -100,6 +100,15 @@
   </si>
   <si>
     <t>&lt; 35000</t>
+  </si>
+  <si>
+    <t>hybrid_rag</t>
+  </si>
+  <si>
+    <t>hybrid_rerank</t>
+  </si>
+  <si>
+    <t>vector_rag</t>
   </si>
 </sst>
 </file>
@@ -165,7 +174,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -215,14 +224,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -556,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
@@ -907,13 +908,386 @@
         <v>24</v>
       </c>
     </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>488</v>
+      </c>
+      <c r="C7">
+        <v>0.93032786885245899</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.82172131147540906</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.86923302107728295</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.75275569717168</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.14707267345587</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.14104072725998901</v>
+      </c>
+      <c r="I7">
+        <v>0.89852887379830004</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1681.6762295081901</v>
+      </c>
+      <c r="K7" s="2">
+        <v>175.97950819672101</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1857.6557377049101</v>
+      </c>
+      <c r="M7" s="2">
+        <v>3.2200741397537498</v>
+      </c>
+      <c r="N7" s="2">
+        <v>5.4682509622950697</v>
+      </c>
+      <c r="O7" s="2">
+        <v>8.6883251020488199</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>488</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.92213114754098302</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.81352459016393397</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.86171935987509696</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.70060100418706905</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.146064221525287</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.13798309500153699</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.89776209949469898</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1661.2848360655701</v>
+      </c>
+      <c r="K8" s="2">
+        <v>172.88319672131101</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1834.1680327868801</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0.39088721577892799</v>
+      </c>
+      <c r="N8" s="2">
+        <v>4.5838559174179201</v>
+      </c>
+      <c r="O8" s="2">
+        <v>4.9747431331968501</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>444</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.88513513513513498</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.75900900900900903</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.81572465322465304</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.66631274131274099</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.14167979792979701</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.13541102916102901</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.89324202704</v>
+      </c>
+      <c r="J9" s="2">
+        <v>2921.8355855855798</v>
+      </c>
+      <c r="K9" s="2">
+        <v>184.13513513513499</v>
+      </c>
+      <c r="L9" s="2">
+        <v>3105.9707207207198</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.17385267567986501</v>
+      </c>
+      <c r="N9" s="2">
+        <v>4.8101293162163703</v>
+      </c>
+      <c r="O9" s="2">
+        <v>4.9839819918962398</v>
+      </c>
+      <c r="P9">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>444</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.92342342342342298</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.80855855855855796</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.85965250965250894</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.73230373230373202</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.14292404917404899</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.13479284104284101</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0.89895509169982302</v>
+      </c>
+      <c r="J10" s="2">
+        <v>2783.5720720720701</v>
+      </c>
+      <c r="K10" s="2">
+        <v>182.40765765765701</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2965.97972972972</v>
+      </c>
+      <c r="M10" s="2">
+        <v>3.2990681218457398</v>
+      </c>
+      <c r="N10" s="2">
+        <v>7.2991731905463304</v>
+      </c>
+      <c r="O10" s="2">
+        <v>10.598241312392</v>
+      </c>
+      <c r="P10">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>444</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.927927927927927</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.80855855855855796</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.860778635778635</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.73651226776226697</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.14398773773773699</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.13735803110803099</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.89575017881286001</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1689.81756756756</v>
+      </c>
+      <c r="K11" s="2">
+        <v>177.79729729729701</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1867.61486486486</v>
+      </c>
+      <c r="M11" s="2">
+        <v>3.25582723063025</v>
+      </c>
+      <c r="N11" s="2">
+        <v>5.3102269288287598</v>
+      </c>
+      <c r="O11">
+        <v>8.5660541594590196</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12">
+        <v>444</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.92117117117117098</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.80180180180180105</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.85477262977262902</v>
+      </c>
+      <c r="F12">
+        <v>0.68200440700440701</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.14963610588610499</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.14188027313027299</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.89559468976012202</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1670.37387387387</v>
+      </c>
+      <c r="K12" s="2">
+        <v>175.68018018018</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1846.0540540540501</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.39444748130660401</v>
+      </c>
+      <c r="N12" s="2">
+        <v>4.5230002536035299</v>
+      </c>
+      <c r="O12" s="2">
+        <v>4.9174477349101302</v>
+      </c>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13">
+        <v>444</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.93693693693693603</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.80855855855855796</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.86581045331045303</v>
+      </c>
+      <c r="F13">
+        <v>0.69836809211809203</v>
+      </c>
+      <c r="G13">
+        <v>0.13574199199199199</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.12873690998690901</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.89505446964018998</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1629.2342342342299</v>
+      </c>
+      <c r="K13" s="2">
+        <v>171.702702702702</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1800.9369369369299</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0.37631118333317498</v>
+      </c>
+      <c r="N13" s="2">
+        <v>4.1284692135132701</v>
+      </c>
+      <c r="O13" s="2">
+        <v>4.5047803968464404</v>
+      </c>
+      <c r="P13">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S13">
+    <sortCondition descending="1" ref="B1:B13"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="top10" dxfId="12" priority="17" rank="1"/>
+    <cfRule type="top10" dxfId="11" priority="17" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="top10" dxfId="11" priority="18" rank="1"/>
     <cfRule type="top10" dxfId="10" priority="19" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
